--- a/ValueSet-mii-vs-mikrobio-bartlett-score-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-bartlett-score-loinc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -123,7 +123,7 @@
     <t>LA21389-4</t>
   </si>
   <si>
-    <t>0 Lack of inflammation and possible contamination with saliva</t>
+    <t>0  Lack of inflammation and possible contamination with saliva</t>
   </si>
   <si>
     <t>LA21388-6</t>

--- a/ValueSet-mii-vs-mikrobio-bartlett-score-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-bartlett-score-loinc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
